--- a/output/2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-01_19_Malesia_Kelantan_Utensilerie_e_Macchine_Utensili.xlsx
@@ -479,7 +479,6 @@
           <t>Gani Machinery &amp; Tools</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -495,7 +494,6 @@
           <t>09-745 3644</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Verificato: hardware/machinery store, Jalan Dato' Lundang, Kota Bharu (fax 09-745 3645). Confermato su più directory (Foursquare, NewPages, BusinessList).</t>
@@ -513,7 +511,6 @@
           <t>Komtar Industry (M) Sdn Bhd (gruppo Komtar Hardware)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -529,7 +526,6 @@
           <t>+6012-223 2739</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Verificato come dealer Makita ufficiale, PT 2460, Jalan 1/44, Kawasan Perindustrian Pengkalan Chepa II, Kota Bharu (fonte: Makita.my Dealers).</t>
@@ -567,7 +563,6 @@
           <t>09-748 5555</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Verificato, Lot 50 Jalan Sultan Yahya Petra, Kota Bharu; dealer power tools/hand tools, fondata 1987/1994.</t>
@@ -575,7 +570,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -585,7 +580,6 @@
           <t>Eng Seng Heng Hardware &amp; Electrical (M) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -601,7 +595,6 @@
           <t>09-744 1089</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Verificato, 3991K Jalan Sultanah Zainab, Kota Bharu. Fornitore hardware/elettrico/engineering industriale.</t>
@@ -619,7 +612,6 @@
           <t>P.K. Chua Enterprise Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -699,7 +691,6 @@
           <t>Krai Chainsaw &amp; Machinery Sdn Bhd</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -737,7 +728,6 @@
           <t>Golden Excel Hardware Trading</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -753,7 +743,6 @@
           <t>014-606 4222</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Verificato, Lot 1764 Taman Mekasar, Pasir Mas. Vende saldatrici, utensili elettrici, profilati metallici/ACP.</t>
@@ -771,7 +760,6 @@
           <t>Kedai Besi Maju Bina</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -787,7 +775,6 @@
           <t>09-950 2580</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
           <t>Verificato (Facebook/Waze), Jalan Ismail Petra, Tanah Merah. Dealer autorizzato power tools con centro assistenza.</t>
@@ -805,7 +792,6 @@
           <t>Syarikat Chang Trading</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -821,7 +807,6 @@
           <t>09-748 4237</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Verificato come centro assistenza autorizzato Bosch Power Tools, 3566-H&amp;I Jalan Sultanah Zainab, Kota Bharu (fax 09-744 9671).</t>
@@ -839,7 +824,6 @@
           <t>Zicsano Machinery Electric</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -855,10 +839,9 @@
           <t>09-744 2004</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Verificato come distributore i-WELD (attrezzature per saldatura), Lot 3991-K Jalan Sultanah Zainab, Kota Bharu.</t>
+          <t>Verificato come distributore i-WELD (attrezzature per saldatura), Lot 3991-K Jalan Sultanah Zainab, Kota Bharu. [DUPLICATO — vedi anche: 2026-10-01_05_Malesia_Kedah_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -873,7 +856,6 @@
           <t>G.M. Maju Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -889,7 +871,6 @@
           <t>09-912 6330</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
           <t>Verificato, dealer autorizzato GL Bosun e DongCheng (utensili elettrici), PT5174 Jalan Kempas 1/2, Gua Musang.</t>
@@ -907,7 +888,6 @@
           <t>Hup Hing Hardware &amp; Engineering Sdn Bhd</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -923,7 +903,6 @@
           <t>09-744 5880</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>Verificato, 5566B Jalan Kuala Krai, Kota Bharu. Attività storica impianti LPG/gas, ampliata a hardware generico/engineering.</t>
@@ -1003,7 +982,6 @@
           <t>09-744 2085</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Verificato, Lot 502-C Jalan Bayam, Kota Bharu. Grossista/dettagliante plumbing, sanitari e hardware; focus principale plumbing/sanitari più che utensili industriali.</t>
@@ -1011,7 +989,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1021,7 +999,6 @@
           <t>Syarikat Shukri Hardware &amp; Welding</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -1037,7 +1014,6 @@
           <t>09-786 7205</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Verificato (Yelp/MyPages), No. 124 Jalan Kota Bharu, area Pasir Puteh.</t>
@@ -1055,7 +1031,6 @@
           <t>Sin Teck Huat Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -1071,7 +1046,6 @@
           <t>09-746 2688</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Verificato, 5701 Kawasan Miel Lundang, Jalan Sultan Yahya Petra, Kota Bharu. Azienda storica (1982), building material &amp; garden equipment dealer.</t>
@@ -1089,7 +1063,6 @@
           <t>Chung Bee Hardware (K.B.) Sdn Bhd</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -1105,7 +1078,6 @@
           <t>09-744 8878</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
           <t>Verificato, No. 1839 Jalan Hospital, Kampung Paya Bemban, Kota Bharu. Tra i principali hardware store della città.</t>
@@ -1123,7 +1095,6 @@
           <t>Tegoh Hardware Trading</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -1139,7 +1110,6 @@
           <t>09-790 0826</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Verificato, Lot 287 Jalan Pasir Pekan, Pasir Mas. Referente: Myusoff Msalleh.</t>
@@ -1157,7 +1127,6 @@
           <t>NY Jaya Trading</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -1173,7 +1142,6 @@
           <t>013 922 8006</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
           <t>Verificato come hardware store in zona Pasir Puteh, Kelantan. Scheda informativa limitata (solo directory tipo Mapcarta).</t>
@@ -1191,7 +1159,6 @@
           <t>Krai Hardware Trading (S.K. Krai Hardware &amp; Trading)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -1207,7 +1174,6 @@
           <t>09-966 6157</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>Verificato con ragione sociale precisa 'S.K. Krai Hardware &amp; Trading', 359 Guchil Satu, Kuala Krai (NewPages/MyPages).</t>
@@ -1225,7 +1191,6 @@
           <t>Gua Musang Hardware Sdn Bhd</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
           <t>Kelantan</t>
@@ -1241,7 +1206,6 @@
           <t>09-912 1760</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>Verificato (Waze/Yelp), PT1939/1940 Jalan Bandar Baru, Gua Musang.</t>
@@ -1279,7 +1243,6 @@
           <t>09-744 9555</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>Verificato, Ground Floor 2678-E Jalan Kuala Krai, Kota Bharu (fax 09-743 1188). Distributore cuscinetti/componenti industriali — categoria adiacente ma coerente come canale B2B industriale.</t>
@@ -1287,7 +1250,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1260,6 @@
           <t>H.E. Trading Machinery Sdn Bhd</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
           <t>Kelantan</t>
